--- a/data/cases/login_cases.xlsx
+++ b/data/cases/login_cases.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,148 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>用户名为空</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A123456</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>账号不存在</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>not-exist@example.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>A123456</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>用户名首尾空格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>3026288915@qq.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A123456</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>密码过短</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3026288915@qq.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>密码全为空格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3026288915@qq.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>fail</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>正确账号大小写邮箱登录</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3026288915@QQ.COM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A123456</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/cases/login_cases.xlsx
+++ b/data/cases/login_cases.xlsx
@@ -588,7 +588,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>用户名首尾空格</t>
+          <t>用户名首尾空格自动去除后登录</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fail</t>
+          <t>success</t>
         </is>
       </c>
       <c r="E8" t="b">
